--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96809942-156E-4BB2-8F0E-B850C7697D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D519360-0D7B-40A5-80C4-2B76AE4C78CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19322" uniqueCount="2669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19327" uniqueCount="2673">
   <si>
     <t>Subfolder Level 1</t>
   </si>
@@ -8034,6 +8034,18 @@
   </si>
   <si>
     <t>doctrine_parameter_divine_marriage_piety_gain_active</t>
+  </si>
+  <si>
+    <t>Compatched</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Should have file</t>
+  </si>
+  <si>
+    <t>Should not have file</t>
   </si>
 </sst>
 </file>
@@ -8077,7 +8089,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8086,6 +8098,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8389,7 +8405,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J604"/>
+  <dimension ref="A1:K604"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -8400,10 +8416,10 @@
     <col min="7" max="7" width="19.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8434,8 +8450,11 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="3" t="s">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -8461,7 +8480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -8487,7 +8506,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -8513,7 +8532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -8539,7 +8558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
@@ -8565,7 +8584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -8591,7 +8610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -8617,7 +8636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -8643,7 +8662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -8669,7 +8688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -8695,7 +8714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
@@ -8718,7 +8737,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -8744,7 +8763,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
@@ -8772,8 +8791,14 @@
       <c r="I14" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="J14" s="1" t="s">
+        <v>2669</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -8799,7 +8824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
@@ -12144,7 +12169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>161</v>
       </c>
@@ -12170,7 +12195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>161</v>
       </c>
@@ -12196,7 +12221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>161</v>
       </c>
@@ -12222,7 +12247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>161</v>
       </c>
@@ -12248,7 +12273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>161</v>
       </c>
@@ -12274,7 +12299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>161</v>
       </c>
@@ -12300,7 +12325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>161</v>
       </c>
@@ -12326,7 +12351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>161</v>
       </c>
@@ -12352,7 +12377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>161</v>
       </c>
@@ -12378,7 +12403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>161</v>
       </c>
@@ -12404,7 +12429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>204</v>
       </c>
@@ -12432,8 +12457,14 @@
       <c r="I155" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="J155" s="4" t="s">
+        <v>2669</v>
+      </c>
+      <c r="K155" s="4" t="s">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>204</v>
       </c>
@@ -12459,7 +12490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>204</v>
       </c>
@@ -12485,7 +12516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>204</v>
       </c>
@@ -12511,7 +12542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>204</v>
       </c>
@@ -12537,7 +12568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>204</v>
       </c>
@@ -12563,7 +12594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>204</v>
       </c>
@@ -12589,7 +12620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>204</v>
       </c>
@@ -12617,8 +12648,9 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K162" s="5"/>
+    </row>
+    <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>204</v>
       </c>
@@ -12644,7 +12676,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>204</v>
       </c>
@@ -12670,7 +12702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>204</v>
       </c>
@@ -12699,7 +12731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>204</v>
       </c>
@@ -12725,7 +12757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>204</v>
       </c>
@@ -12751,7 +12783,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>204</v>
       </c>
@@ -12777,7 +12809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>204</v>
       </c>
@@ -12803,7 +12835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>204</v>
       </c>
@@ -12829,7 +12861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>204</v>
       </c>
@@ -12855,7 +12887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>204</v>
       </c>
@@ -12881,7 +12913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>204</v>
       </c>
@@ -12907,7 +12939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>204</v>
       </c>
@@ -12936,7 +12968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>204</v>
       </c>
@@ -12962,7 +12994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>204</v>
       </c>
@@ -24125,6 +24157,7 @@
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D519360-0D7B-40A5-80C4-2B76AE4C78CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349A5955-A431-40A5-B771-AAA74029F940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19327" uniqueCount="2673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19329" uniqueCount="2674">
   <si>
     <t>Subfolder Level 1</t>
   </si>
@@ -8046,6 +8046,9 @@
   </si>
   <si>
     <t>Should not have file</t>
+  </si>
+  <si>
+    <t>No issues. Fixed calyver_on_death_on_action instead.</t>
   </si>
 </sst>
 </file>
@@ -8089,7 +8092,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8101,7 +8104,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12457,10 +12459,10 @@
       <c r="I155" s="1">
         <v>0</v>
       </c>
-      <c r="J155" s="4" t="s">
+      <c r="J155" s="1" t="s">
         <v>2669</v>
       </c>
-      <c r="K155" s="4" t="s">
+      <c r="K155" s="1" t="s">
         <v>2672</v>
       </c>
     </row>
@@ -12648,7 +12650,9 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
-      <c r="K162" s="5"/>
+      <c r="K162" t="s">
+        <v>2673</v>
+      </c>
     </row>
     <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
@@ -12715,7 +12719,7 @@
       <c r="D165" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E165" s="1" t="s">
+      <c r="E165" s="4" t="s">
         <v>219</v>
       </c>
       <c r="F165" s="1" t="s">
@@ -12729,6 +12733,9 @@
       </c>
       <c r="I165" s="1">
         <v>0</v>
+      </c>
+      <c r="K165" s="4" t="s">
+        <v>2672</v>
       </c>
     </row>
     <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.3">

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349A5955-A431-40A5-B771-AAA74029F940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9E58D1-C115-4815-80A8-7882E69BCA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19329" uniqueCount="2674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19330" uniqueCount="2674">
   <si>
     <t>Subfolder Level 1</t>
   </si>
@@ -8042,13 +8042,13 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Should have file</t>
-  </si>
-  <si>
     <t>Should not have file</t>
   </si>
   <si>
     <t>No issues. Fixed calyver_on_death_on_action instead.</t>
+  </si>
+  <si>
+    <t>Fixed. New file</t>
   </si>
 </sst>
 </file>
@@ -8092,7 +8092,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8101,9 +8101,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8796,8 +8793,8 @@
       <c r="J14" s="1" t="s">
         <v>2669</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>2671</v>
+      <c r="K14" t="s">
+        <v>2673</v>
       </c>
     </row>
     <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
@@ -12463,7 +12460,7 @@
         <v>2669</v>
       </c>
       <c r="K155" s="1" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
     </row>
     <row r="156" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
@@ -12651,7 +12648,7 @@
         <v>0</v>
       </c>
       <c r="K162" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
@@ -12719,7 +12716,7 @@
       <c r="D165" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="E165" s="4" t="s">
+      <c r="E165" s="1" t="s">
         <v>219</v>
       </c>
       <c r="F165" s="1" t="s">
@@ -12734,8 +12731,8 @@
       <c r="I165" s="1">
         <v>0</v>
       </c>
-      <c r="K165" s="4" t="s">
-        <v>2672</v>
+      <c r="K165" s="1" t="s">
+        <v>2671</v>
       </c>
     </row>
     <row r="166" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
@@ -12973,6 +12970,9 @@
       </c>
       <c r="I174" s="1">
         <v>0</v>
+      </c>
+      <c r="K174" t="s">
+        <v>2673</v>
       </c>
     </row>
     <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.3">

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9E58D1-C115-4815-80A8-7882E69BCA03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0FF901-5B6F-450E-8707-A525155126D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19330" uniqueCount="2674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19331" uniqueCount="2674">
   <si>
     <t>Subfolder Level 1</t>
   </si>
@@ -13029,6 +13029,9 @@
       <c r="I176" s="1">
         <v>0</v>
       </c>
+      <c r="K176" t="s">
+        <v>2673</v>
+      </c>
     </row>
     <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0FF901-5B6F-450E-8707-A525155126D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C819CF12-6994-4F36-829E-B5104E73B5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19331" uniqueCount="2674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19337" uniqueCount="2674">
   <si>
     <t>Subfolder Level 1</t>
   </si>
@@ -8045,10 +8045,10 @@
     <t>Should not have file</t>
   </si>
   <si>
-    <t>No issues. Fixed calyver_on_death_on_action instead.</t>
-  </si>
-  <si>
     <t>Fixed. New file</t>
+  </si>
+  <si>
+    <t>No issues. Fixed calyver_on_death_on_action instead. So, file created.</t>
   </si>
 </sst>
 </file>
@@ -8794,7 +8794,7 @@
         <v>2669</v>
       </c>
       <c r="K14" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
@@ -12647,8 +12647,11 @@
       <c r="I162" s="1">
         <v>0</v>
       </c>
+      <c r="J162" s="1" t="s">
+        <v>2669</v>
+      </c>
       <c r="K162" t="s">
-        <v>2672</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="163" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
@@ -12731,6 +12734,9 @@
       <c r="I165" s="1">
         <v>0</v>
       </c>
+      <c r="J165" s="1" t="s">
+        <v>2669</v>
+      </c>
       <c r="K165" s="1" t="s">
         <v>2671</v>
       </c>
@@ -12971,8 +12977,11 @@
       <c r="I174" s="1">
         <v>0</v>
       </c>
+      <c r="J174" s="1" t="s">
+        <v>2669</v>
+      </c>
       <c r="K174" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="175" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
@@ -13029,8 +13038,11 @@
       <c r="I176" s="1">
         <v>0</v>
       </c>
+      <c r="J176" s="1" t="s">
+        <v>2669</v>
+      </c>
       <c r="K176" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
@@ -17193,7 +17205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" s="1" t="s">
         <v>346</v>
       </c>
@@ -17219,7 +17231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" s="1" t="s">
         <v>346</v>
       </c>
@@ -17245,7 +17257,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" s="1" t="s">
         <v>346</v>
       </c>
@@ -17271,7 +17283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>346</v>
       </c>
@@ -17294,7 +17306,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" s="1" t="s">
         <v>346</v>
       </c>
@@ -17322,8 +17334,14 @@
       <c r="I341" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="J341" s="1" t="s">
+        <v>2669</v>
+      </c>
+      <c r="K341" t="s">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="342" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" s="1" t="s">
         <v>346</v>
       </c>
@@ -17349,7 +17367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>346</v>
       </c>
@@ -17375,7 +17393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>346</v>
       </c>
@@ -17401,7 +17419,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>346</v>
       </c>
@@ -17427,7 +17445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" s="1" t="s">
         <v>346</v>
       </c>
@@ -17453,7 +17471,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>346</v>
       </c>
@@ -17479,7 +17497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" s="1" t="s">
         <v>346</v>
       </c>
@@ -17505,7 +17523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>346</v>
       </c>
@@ -17531,7 +17549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1" t="s">
         <v>346</v>
       </c>
@@ -17557,7 +17575,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1" t="s">
         <v>346</v>
       </c>
@@ -17583,7 +17601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1" t="s">
         <v>346</v>
       </c>

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C819CF12-6994-4F36-829E-B5104E73B5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B0DD9F-880E-4458-AC41-4F1719219AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B0DD9F-880E-4458-AC41-4F1719219AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2764E5E-13E8-4D62-A002-E6A8CA20A539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19337" uniqueCount="2674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19339" uniqueCount="2674">
   <si>
     <t>Subfolder Level 1</t>
   </si>
@@ -18459,7 +18459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>465</v>
       </c>
@@ -18485,7 +18485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>465</v>
       </c>
@@ -18511,7 +18511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>469</v>
       </c>
@@ -18537,7 +18537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>469</v>
       </c>
@@ -18565,8 +18565,14 @@
       <c r="I388" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="J388" s="1" t="s">
+        <v>2669</v>
+      </c>
+      <c r="K388" t="s">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="389" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>469</v>
       </c>
@@ -18592,7 +18598,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>469</v>
       </c>
@@ -18618,7 +18624,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>477</v>
       </c>
@@ -18644,7 +18650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>477</v>
       </c>
@@ -18670,7 +18676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>477</v>
       </c>
@@ -18696,7 +18702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>477</v>
       </c>
@@ -18722,7 +18728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>477</v>
       </c>
@@ -18748,7 +18754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>477</v>
       </c>
@@ -18774,7 +18780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>477</v>
       </c>
@@ -18800,7 +18806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>477</v>
       </c>
@@ -18826,7 +18832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>477</v>
       </c>
@@ -18852,7 +18858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>477</v>
       </c>

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2764E5E-13E8-4D62-A002-E6A8CA20A539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49030E3-E585-4C6B-BCE9-E6151C0B7C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19339" uniqueCount="2674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19346" uniqueCount="2677">
   <si>
     <t>Subfolder Level 1</t>
   </si>
@@ -8049,6 +8049,15 @@
   </si>
   <si>
     <t>No issues. Fixed calyver_on_death_on_action instead. So, file created.</t>
+  </si>
+  <si>
+    <t>court_scheme_marriage_effect</t>
+  </si>
+  <si>
+    <t>zz_lmfmod_effects</t>
+  </si>
+  <si>
+    <t>LMF</t>
   </si>
 </sst>
 </file>
@@ -8404,7 +8413,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:K604"/>
+  <dimension ref="A1:K605"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -24180,6 +24189,35 @@
       </c>
       <c r="I604" s="1">
         <v>2</v>
+      </c>
+    </row>
+    <row r="605" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A605" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B605" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C605" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D605" s="1" t="s">
+        <v>2675</v>
+      </c>
+      <c r="E605" s="1" t="s">
+        <v>2674</v>
+      </c>
+      <c r="F605" s="1" t="s">
+        <v>2676</v>
+      </c>
+      <c r="G605" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H605" s="1">
+        <v>154</v>
+      </c>
+      <c r="I605" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49030E3-E585-4C6B-BCE9-E6151C0B7C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2F40C4-46DF-413C-9734-69D1F8463B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
-    <sheet name="events" sheetId="2" r:id="rId2"/>
-    <sheet name="localization" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja1" sheetId="4" r:id="rId2"/>
+    <sheet name="events" sheetId="2" r:id="rId3"/>
+    <sheet name="localization" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">common!$A$1:$J$604</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">events!$A$1:$J$394</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">localization!$A$1:$J$1660</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">events!$A$1:$J$394</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">localization!$A$1:$J$1660</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19346" uniqueCount="2677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19367" uniqueCount="2687">
   <si>
     <t>Subfolder Level 1</t>
   </si>
@@ -8058,6 +8059,36 @@
   </si>
   <si>
     <t>LMF</t>
+  </si>
+  <si>
+    <t>Compatched on the polygamy faith doctrine side.</t>
+  </si>
+  <si>
+    <t>ansf.2101</t>
+  </si>
+  <si>
+    <t>ansf.2301</t>
+  </si>
+  <si>
+    <t>Check polygamy culture tradition (tradition_polygamous)</t>
+  </si>
+  <si>
+    <t>Check polygamy faith doctrine (doctrine_polygamy)</t>
+  </si>
+  <si>
+    <t>Check concubines faith doctrine (doctrine_concubines)</t>
+  </si>
+  <si>
+    <t>Check concubines culture tradition (tradition_concubines)</t>
+  </si>
+  <si>
+    <t>Does not appear</t>
+  </si>
+  <si>
+    <t>Check Japanese house (or tradition that allows for polygamy) (tradition_tgp_japanese_houses)</t>
+  </si>
+  <si>
+    <t>Check for court machinations (tradition_tgp_court_machinations)</t>
   </si>
 </sst>
 </file>
@@ -8101,7 +8132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8110,11 +8141,105 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -8413,7 +8538,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:K605"/>
+  <dimension ref="A1:K617"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -23879,7 +24004,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" s="1" t="s">
         <v>616</v>
       </c>
@@ -23905,7 +24030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
         <v>616</v>
       </c>
@@ -23931,7 +24056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="1" t="s">
         <v>616</v>
       </c>
@@ -23957,7 +24082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="1" t="s">
         <v>616</v>
       </c>
@@ -23983,7 +24108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="1" t="s">
         <v>695</v>
       </c>
@@ -24009,7 +24134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
         <v>695</v>
       </c>
@@ -24035,7 +24160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="1" t="s">
         <v>695</v>
       </c>
@@ -24061,7 +24186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="1" t="s">
         <v>695</v>
       </c>
@@ -24087,7 +24212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="1" t="s">
         <v>695</v>
       </c>
@@ -24113,7 +24238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="1" t="s">
         <v>695</v>
       </c>
@@ -24139,7 +24264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="603" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" s="1" t="s">
         <v>695</v>
       </c>
@@ -24165,7 +24290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="604" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
         <v>695</v>
       </c>
@@ -24191,7 +24316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A605" s="1" t="s">
         <v>346</v>
       </c>
@@ -24204,7 +24329,7 @@
       <c r="D605" s="1" t="s">
         <v>2675</v>
       </c>
-      <c r="E605" s="1" t="s">
+      <c r="E605" s="4" t="s">
         <v>2674</v>
       </c>
       <c r="F605" s="1" t="s">
@@ -24219,6 +24344,12 @@
       <c r="I605" s="1">
         <v>3</v>
       </c>
+      <c r="K605" t="s">
+        <v>2677</v>
+      </c>
+    </row>
+    <row r="617" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E617" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J604" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -24234,6 +24365,146 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88C6B958-49F1-4824-A195-E0276EAACA8E}">
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>2684</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="2" id="{DD2C4D04-4395-4295-BF66-C9402D47E898}">
+            <xm:f>COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") &gt; 0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF00B050"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="1" id="{A73F0FB6-DD42-4661-8925-0B0E5922E3F5}">
+            <xm:f>AND(B3&lt;&gt;"", COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") = 0)</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC00000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>B3:B24</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:J394"/>
@@ -34512,7 +34783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:J1660"/>

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2F40C4-46DF-413C-9734-69D1F8463B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B269CB-473F-4957-B5B1-CC4652C73A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19367" uniqueCount="2687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19368" uniqueCount="2686">
   <si>
     <t>Subfolder Level 1</t>
   </si>
@@ -8059,9 +8059,6 @@
   </si>
   <si>
     <t>LMF</t>
-  </si>
-  <si>
-    <t>Compatched on the polygamy faith doctrine side.</t>
   </si>
   <si>
     <t>ansf.2101</t>
@@ -8141,14 +8138,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -8160,82 +8155,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8538,7 +8457,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:K617"/>
+  <dimension ref="A1:K605"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -18702,7 +18621,7 @@
       <c r="J388" s="1" t="s">
         <v>2669</v>
       </c>
-      <c r="K388" t="s">
+      <c r="K388" s="4" t="s">
         <v>2672</v>
       </c>
     </row>
@@ -24329,7 +24248,7 @@
       <c r="D605" s="1" t="s">
         <v>2675</v>
       </c>
-      <c r="E605" s="4" t="s">
+      <c r="E605" s="1" t="s">
         <v>2674</v>
       </c>
       <c r="F605" s="1" t="s">
@@ -24344,12 +24263,12 @@
       <c r="I605" s="1">
         <v>3</v>
       </c>
+      <c r="J605" s="1" t="s">
+        <v>2669</v>
+      </c>
       <c r="K605" t="s">
-        <v>2677</v>
-      </c>
-    </row>
-    <row r="617" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E617" s="4"/>
+        <v>2672</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J604" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -24376,7 +24295,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -24396,7 +24315,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -24411,17 +24330,17 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
+        <v>2677</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B10" s="4" t="s">
         <v>2678</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>2679</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -24441,32 +24360,32 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
     </row>
   </sheetData>
@@ -24476,22 +24395,22 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{A73F0FB6-DD42-4661-8925-0B0E5922E3F5}">
+            <xm:f>AND(B3&lt;&gt;"", COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") = 0)</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC00000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
           <x14:cfRule type="expression" priority="2" id="{DD2C4D04-4395-4295-BF66-C9402D47E898}">
             <xm:f>COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") &gt; 0</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
                   <bgColor rgb="FF00B050"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="1" id="{A73F0FB6-DD42-4661-8925-0B0E5922E3F5}">
-            <xm:f>AND(B3&lt;&gt;"", COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") = 0)</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFC00000"/>
                 </patternFill>
               </fill>
             </x14:dxf>

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{290BACAC-1747-43AE-B0EE-8C16181BD4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137B9260-FFFC-47F4-B801-161E5682963D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -8092,7 +8092,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8102,14 +8102,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -8146,7 +8138,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137B9260-FFFC-47F4-B801-161E5682963D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB0443B-4195-4362-B9C6-BA96A34EE057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,25 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">events!$A$1:$J$394</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">localization!$A$1:$J$1660</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19368" uniqueCount="2686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19382" uniqueCount="2687">
   <si>
     <t>Subfolder Level 1</t>
   </si>
@@ -8086,6 +8099,9 @@
   </si>
   <si>
     <t>Check for court machinations (tradition_tgp_court_machinations)</t>
+  </si>
+  <si>
+    <t>zz_ansf_events</t>
   </si>
 </sst>
 </file>
@@ -8129,7 +8145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8138,7 +8154,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -24334,7 +24349,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B10" s="4" t="s">
+      <c r="B10" t="s">
         <v>2678</v>
       </c>
     </row>
@@ -24426,7 +24441,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J394"/>
+  <dimension ref="A1:J396"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -34688,6 +34703,66 @@
       </c>
       <c r="I394" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A395" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>2686</v>
+      </c>
+      <c r="E395" s="1" t="s">
+        <v>2677</v>
+      </c>
+      <c r="F395" s="1" t="s">
+        <v>2676</v>
+      </c>
+      <c r="G395" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H395" s="1">
+        <f>6826-6568+1</f>
+        <v>259</v>
+      </c>
+      <c r="I395" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A396" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>2686</v>
+      </c>
+      <c r="E396" s="1" t="s">
+        <v>2678</v>
+      </c>
+      <c r="F396" s="1" t="s">
+        <v>2676</v>
+      </c>
+      <c r="G396" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H396" s="1">
+        <f>13544-13294+1</f>
+        <v>251</v>
+      </c>
+      <c r="I396" s="1">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB0443B-4195-4362-B9C6-BA96A34EE057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC87A3F3-2D5A-4151-81FC-FCED203DEE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19382" uniqueCount="2687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19387" uniqueCount="2687">
   <si>
     <t>Subfolder Level 1</t>
   </si>
@@ -8158,7 +8158,63 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -24410,22 +24466,22 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" id="{A73F0FB6-DD42-4661-8925-0B0E5922E3F5}">
-            <xm:f>AND(B3&lt;&gt;"", COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") = 0)</xm:f>
+          <x14:cfRule type="expression" priority="2" id="{B9E699C7-1B8D-420A-919A-B98193DF32DA}">
+            <xm:f>(COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") + COUNTIFS(events!$E:$E, B3, events!$J:$J, "compatched")) &gt; 0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF00B050"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="1" id="{EC430BDE-D243-42C6-A175-B9E6C3A90E8C}">
+            <xm:f>AND(B3&lt;&gt;"", (COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") + COUNTIFS(events!$E:$E, B3, events!$J:$J, "compatched")) = 0)</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
                   <bgColor rgb="FFC00000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="2" id="{DD2C4D04-4395-4295-BF66-C9402D47E898}">
-            <xm:f>COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") &gt; 0</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF00B050"/>
                 </patternFill>
               </fill>
             </x14:dxf>
@@ -24441,7 +24497,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J396"/>
+  <dimension ref="A1:K396"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -24452,10 +24508,11 @@
     <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -24486,8 +24543,11 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="3" t="s">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>705</v>
       </c>
@@ -24510,7 +24570,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>707</v>
       </c>
@@ -24536,7 +24596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>707</v>
       </c>
@@ -24562,7 +24622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>707</v>
       </c>
@@ -24588,7 +24648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>707</v>
       </c>
@@ -24614,7 +24674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>707</v>
       </c>
@@ -24640,7 +24700,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>707</v>
       </c>
@@ -24666,7 +24726,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>707</v>
       </c>
@@ -24692,7 +24752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>707</v>
       </c>
@@ -24718,7 +24778,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>707</v>
       </c>
@@ -24744,7 +24804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>707</v>
       </c>
@@ -24770,7 +24830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>707</v>
       </c>
@@ -24796,7 +24856,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>707</v>
       </c>
@@ -24822,7 +24882,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>707</v>
       </c>
@@ -24848,7 +24908,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>707</v>
       </c>
@@ -34445,7 +34505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34471,7 +34531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34497,7 +34557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34523,7 +34583,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34549,7 +34609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34575,7 +34635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34601,7 +34661,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34627,7 +34687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34653,7 +34713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34679,7 +34739,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34705,7 +34765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>12</v>
       </c>
@@ -34734,8 +34794,14 @@
       <c r="I395" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J395" s="1" t="s">
+        <v>2669</v>
+      </c>
+      <c r="K395" t="s">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" s="1" t="s">
         <v>12</v>
       </c>
@@ -34763,6 +34829,12 @@
       </c>
       <c r="I396" s="1">
         <v>4</v>
+      </c>
+      <c r="J396" s="1" t="s">
+        <v>2669</v>
+      </c>
+      <c r="K396" t="s">
+        <v>2672</v>
       </c>
     </row>
   </sheetData>

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B269CB-473F-4957-B5B1-CC4652C73A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC87A3F3-2D5A-4151-81FC-FCED203DEE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,12 +23,25 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">events!$A$1:$J$394</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">localization!$A$1:$J$1660</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19368" uniqueCount="2686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19387" uniqueCount="2687">
   <si>
     <t>Subfolder Level 1</t>
   </si>
@@ -8086,6 +8099,9 @@
   </si>
   <si>
     <t>Check for court machinations (tradition_tgp_court_machinations)</t>
+  </si>
+  <si>
+    <t>zz_ansf_events</t>
   </si>
 </sst>
 </file>
@@ -8129,7 +8145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -8138,7 +8154,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18621,7 +18636,7 @@
       <c r="J388" s="1" t="s">
         <v>2669</v>
       </c>
-      <c r="K388" s="4" t="s">
+      <c r="K388" t="s">
         <v>2672</v>
       </c>
     </row>
@@ -24334,7 +24349,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B10" s="4" t="s">
+      <c r="B10" t="s">
         <v>2678</v>
       </c>
     </row>
@@ -24395,8 +24410,8 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="1" id="{A73F0FB6-DD42-4661-8925-0B0E5922E3F5}">
-            <xm:f>AND(B3&lt;&gt;"", COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") = 0)</xm:f>
+          <x14:cfRule type="expression" priority="1" id="{EC430BDE-D243-42C6-A175-B9E6C3A90E8C}">
+            <xm:f>AND(B3&lt;&gt;"", (COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") + COUNTIFS(events!$E:$E, B3, events!$J:$J, "compatched")) = 0)</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -24405,8 +24420,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="2" id="{DD2C4D04-4395-4295-BF66-C9402D47E898}">
-            <xm:f>COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") &gt; 0</xm:f>
+          <x14:cfRule type="expression" priority="2" id="{B9E699C7-1B8D-420A-919A-B98193DF32DA}">
+            <xm:f>(COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") + COUNTIFS(events!$E:$E, B3, events!$J:$J, "compatched")) &gt; 0</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -24426,7 +24441,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:J394"/>
+  <dimension ref="A1:K396"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -24437,10 +24452,11 @@
     <col min="7" max="7" width="14.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -24471,8 +24487,11 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="K1" s="3" t="s">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>705</v>
       </c>
@@ -24495,7 +24514,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>707</v>
       </c>
@@ -24521,7 +24540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>707</v>
       </c>
@@ -24547,7 +24566,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>707</v>
       </c>
@@ -24573,7 +24592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>707</v>
       </c>
@@ -24599,7 +24618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>707</v>
       </c>
@@ -24625,7 +24644,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>707</v>
       </c>
@@ -24651,7 +24670,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>707</v>
       </c>
@@ -24677,7 +24696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>707</v>
       </c>
@@ -24703,7 +24722,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>707</v>
       </c>
@@ -24729,7 +24748,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>707</v>
       </c>
@@ -24755,7 +24774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>707</v>
       </c>
@@ -24781,7 +24800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>707</v>
       </c>
@@ -24807,7 +24826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>707</v>
       </c>
@@ -24833,7 +24852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>707</v>
       </c>
@@ -34430,7 +34449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34456,7 +34475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34482,7 +34501,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34508,7 +34527,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34534,7 +34553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34560,7 +34579,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34586,7 +34605,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34612,7 +34631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34638,7 +34657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34664,7 +34683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>1110</v>
       </c>
@@ -34688,6 +34707,78 @@
       </c>
       <c r="I394" s="1">
         <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A395" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B395" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D395" s="1" t="s">
+        <v>2686</v>
+      </c>
+      <c r="E395" s="1" t="s">
+        <v>2677</v>
+      </c>
+      <c r="F395" s="1" t="s">
+        <v>2676</v>
+      </c>
+      <c r="G395" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H395" s="1">
+        <f>6826-6568+1</f>
+        <v>259</v>
+      </c>
+      <c r="I395" s="1">
+        <v>4</v>
+      </c>
+      <c r="J395" s="1" t="s">
+        <v>2669</v>
+      </c>
+      <c r="K395" t="s">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A396" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B396" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D396" s="1" t="s">
+        <v>2686</v>
+      </c>
+      <c r="E396" s="1" t="s">
+        <v>2678</v>
+      </c>
+      <c r="F396" s="1" t="s">
+        <v>2676</v>
+      </c>
+      <c r="G396" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H396" s="1">
+        <f>13544-13294+1</f>
+        <v>251</v>
+      </c>
+      <c r="I396" s="1">
+        <v>4</v>
+      </c>
+      <c r="J396" s="1" t="s">
+        <v>2669</v>
+      </c>
+      <c r="K396" t="s">
+        <v>2672</v>
       </c>
     </row>
   </sheetData>

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC87A3F3-2D5A-4151-81FC-FCED203DEE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>

--- a/mod_compatch_database.xlsx
+++ b/mod_compatch_database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Documents\Paradox Interactive\Crusader Kings III\mod\Harem-Politics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC87A3F3-2D5A-4151-81FC-FCED203DEE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42EB860F-6DF5-4F32-9ADD-5911CBE38D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="common" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19387" uniqueCount="2687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19394" uniqueCount="2693">
   <si>
     <t>Subfolder Level 1</t>
   </si>
@@ -8102,6 +8102,24 @@
   </si>
   <si>
     <t>zz_ansf_events</t>
+  </si>
+  <si>
+    <t>Divorces opinion (divorced_me_opinion)</t>
+  </si>
+  <si>
+    <t>Made secondary opinion (spouse_made_secondary_opinion)</t>
+  </si>
+  <si>
+    <t>Set me aside opinion (set_me_aside_opinion)</t>
+  </si>
+  <si>
+    <t>could_be_introduced_character_trigger</t>
+  </si>
+  <si>
+    <t>can_elope_character_trigger</t>
+  </si>
+  <si>
+    <t>lmf_birth.1008</t>
   </si>
 </sst>
 </file>
@@ -8158,63 +8176,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -24356,7 +24318,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88C6B958-49F1-4824-A195-E0276EAACA8E}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -24457,6 +24419,41 @@
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>2683</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>2691</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>2692</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>2689</v>
       </c>
     </row>
   </sheetData>
@@ -24466,22 +24463,22 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{EC430BDE-D243-42C6-A175-B9E6C3A90E8C}">
+            <xm:f>AND(B3&lt;&gt;"", (COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") + COUNTIFS(events!$E:$E, B3, events!$J:$J, "compatched")) = 0)</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFC00000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
           <x14:cfRule type="expression" priority="2" id="{B9E699C7-1B8D-420A-919A-B98193DF32DA}">
             <xm:f>(COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") + COUNTIFS(events!$E:$E, B3, events!$J:$J, "compatched")) &gt; 0</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
                   <bgColor rgb="FF00B050"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="1" id="{EC430BDE-D243-42C6-A175-B9E6C3A90E8C}">
-            <xm:f>AND(B3&lt;&gt;"", (COUNTIFS(common!$E:$E, B3, common!$J:$J, "compatched") + COUNTIFS(events!$E:$E, B3, events!$J:$J, "compatched")) = 0)</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFC00000"/>
                 </patternFill>
               </fill>
             </x14:dxf>
